--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/30.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/30.xlsx
@@ -426,13 +426,13 @@
         <v>-20.20744407489086</v>
       </c>
       <c r="E2">
-        <v>-15.86894334587851</v>
+        <v>-14.23347137258634</v>
       </c>
       <c r="F2">
-        <v>-2.104814697855677</v>
+        <v>-2.404391676232033</v>
       </c>
       <c r="G2">
-        <v>-13.50305760679319</v>
+        <v>-13.08430339098524</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-19.7238252575516</v>
       </c>
       <c r="E3">
-        <v>-15.81694740732244</v>
+        <v>-14.084493634682</v>
       </c>
       <c r="F3">
-        <v>-1.912331080893166</v>
+        <v>-2.492657941723135</v>
       </c>
       <c r="G3">
-        <v>-13.57767895852113</v>
+        <v>-12.41925782923767</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.18783878456492</v>
       </c>
       <c r="E4">
-        <v>-17.81405425791915</v>
+        <v>-14.90877100203217</v>
       </c>
       <c r="F4">
-        <v>-2.148618419770816</v>
+        <v>-2.621013346904714</v>
       </c>
       <c r="G4">
-        <v>-12.07444795859488</v>
+        <v>-11.83946874676295</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.67052704282876</v>
       </c>
       <c r="E5">
-        <v>-17.6057353966183</v>
+        <v>-16.54086926218863</v>
       </c>
       <c r="F5">
-        <v>-1.819190960447299</v>
+        <v>-2.577462226083087</v>
       </c>
       <c r="G5">
-        <v>-11.84001167623139</v>
+        <v>-11.86320535827952</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.16458663791069</v>
       </c>
       <c r="E6">
-        <v>-18.72468509612159</v>
+        <v>-17.92879673232551</v>
       </c>
       <c r="F6">
-        <v>-1.905476801691144</v>
+        <v>-2.522146545868618</v>
       </c>
       <c r="G6">
-        <v>-11.87439500220226</v>
+        <v>-11.89830045154134</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.68935076293567</v>
       </c>
       <c r="E7">
-        <v>-18.03085947951038</v>
+        <v>-17.85886803669906</v>
       </c>
       <c r="F7">
-        <v>-2.061364934212638</v>
+        <v>-2.399681734839517</v>
       </c>
       <c r="G7">
-        <v>-10.61737092930437</v>
+        <v>-11.12855888711431</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.24562965790753</v>
       </c>
       <c r="E8">
-        <v>-19.86183926113571</v>
+        <v>-18.47067393208334</v>
       </c>
       <c r="F8">
-        <v>-1.887947552766103</v>
+        <v>-2.618912561007884</v>
       </c>
       <c r="G8">
-        <v>-11.93179986185322</v>
+        <v>-10.21322946150676</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.83192264700397</v>
       </c>
       <c r="E9">
-        <v>-20.60430974553731</v>
+        <v>-19.03809172524444</v>
       </c>
       <c r="F9">
-        <v>-1.875258900971602</v>
+        <v>-2.360631506229568</v>
       </c>
       <c r="G9">
-        <v>-11.62683240677556</v>
+        <v>-9.735683267466895</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.44757355324495</v>
       </c>
       <c r="E10">
-        <v>-20.1271534962971</v>
+        <v>-18.58203816487997</v>
       </c>
       <c r="F10">
-        <v>-1.967995176409032</v>
+        <v>-2.733393910517255</v>
       </c>
       <c r="G10">
-        <v>-10.21043536107162</v>
+        <v>-10.04742740926344</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.07374557305643</v>
       </c>
       <c r="E11">
-        <v>-21.04020253961962</v>
+        <v>-19.27831368592933</v>
       </c>
       <c r="F11">
-        <v>-1.258203524403719</v>
+        <v>-2.222796037438169</v>
       </c>
       <c r="G11">
-        <v>-9.779193767489536</v>
+        <v>-9.425127611518942</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.7005318515886</v>
       </c>
       <c r="E12">
-        <v>-21.51542965893257</v>
+        <v>-18.2675582874173</v>
       </c>
       <c r="F12">
-        <v>-1.548656773001229</v>
+        <v>-1.872339339116489</v>
       </c>
       <c r="G12">
-        <v>-10.76352158322658</v>
+        <v>-8.221472843259646</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.29704124332667</v>
       </c>
       <c r="E13">
-        <v>-22.71699683823179</v>
+        <v>-21.79914308398712</v>
       </c>
       <c r="F13">
-        <v>-1.557293513211078</v>
+        <v>-2.292791879635804</v>
       </c>
       <c r="G13">
-        <v>-8.665675222627975</v>
+        <v>-8.331823257720172</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.8501274960348</v>
       </c>
       <c r="E14">
-        <v>-23.80446005795974</v>
+        <v>-22.21795900258651</v>
       </c>
       <c r="F14">
-        <v>-1.241303798580064</v>
+        <v>-1.927730245361942</v>
       </c>
       <c r="G14">
-        <v>-8.753835050338767</v>
+        <v>-8.50744769857851</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.34730424433451</v>
       </c>
       <c r="E15">
-        <v>-23.65300977324721</v>
+        <v>-23.26124242989563</v>
       </c>
       <c r="F15">
-        <v>-1.094496635777701</v>
+        <v>-2.001618044846769</v>
       </c>
       <c r="G15">
-        <v>-8.07491499223611</v>
+        <v>-6.21690110323001</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.78531271991673</v>
       </c>
       <c r="E16">
-        <v>-24.85788726704604</v>
+        <v>-25.1748396913169</v>
       </c>
       <c r="F16">
-        <v>-0.8541035393142737</v>
+        <v>-1.678386043064451</v>
       </c>
       <c r="G16">
-        <v>-7.611034730182353</v>
+        <v>-7.659428284875419</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.17989565649114</v>
       </c>
       <c r="E17">
-        <v>-25.07798468924085</v>
+        <v>-24.78985600202881</v>
       </c>
       <c r="F17">
-        <v>-0.9150081177043285</v>
+        <v>-1.474137074856141</v>
       </c>
       <c r="G17">
-        <v>-7.514644886260934</v>
+        <v>-7.097155298848984</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.54093459917623</v>
       </c>
       <c r="E18">
-        <v>-26.21186929602143</v>
+        <v>-25.35810250593331</v>
       </c>
       <c r="F18">
-        <v>-0.6447407847050096</v>
+        <v>-1.288905247280428</v>
       </c>
       <c r="G18">
-        <v>-7.60582393150354</v>
+        <v>-5.63238787227075</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.89492082942667</v>
       </c>
       <c r="E19">
-        <v>-27.00410770976733</v>
+        <v>-25.50907277240102</v>
       </c>
       <c r="F19">
-        <v>-0.4648017022986951</v>
+        <v>-1.025329863626798</v>
       </c>
       <c r="G19">
-        <v>-6.719054582263282</v>
+        <v>-5.822552229137566</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.25310127397001</v>
       </c>
       <c r="E20">
-        <v>-28.40492321693003</v>
+        <v>-26.35374185820773</v>
       </c>
       <c r="F20">
-        <v>-0.04350742208532415</v>
+        <v>-0.8766293804025267</v>
       </c>
       <c r="G20">
-        <v>-6.891474415039603</v>
+        <v>-5.469095213546199</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.63635897192693</v>
       </c>
       <c r="E21">
-        <v>-28.06628845911045</v>
+        <v>-26.57829077035207</v>
       </c>
       <c r="F21">
-        <v>-0.1366206195306287</v>
+        <v>-0.6819040277167118</v>
       </c>
       <c r="G21">
-        <v>-7.51816068562364</v>
+        <v>-5.735488192000273</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.06046356075946</v>
       </c>
       <c r="E22">
-        <v>-28.60650370890747</v>
+        <v>-28.09915159498412</v>
       </c>
       <c r="F22">
-        <v>0.1574513970836605</v>
+        <v>-0.5645442927060292</v>
       </c>
       <c r="G22">
-        <v>-6.383434786037508</v>
+        <v>-5.068942953123412</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.536567611745003</v>
       </c>
       <c r="E23">
-        <v>-28.97733591692159</v>
+        <v>-29.16499135132544</v>
       </c>
       <c r="F23">
-        <v>0.5536724452437941</v>
+        <v>-0.5586853726718609</v>
       </c>
       <c r="G23">
-        <v>-7.074239702626148</v>
+        <v>-5.534746642135485</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.082161203285253</v>
       </c>
       <c r="E24">
-        <v>-30.56914434383181</v>
+        <v>-29.22834017421874</v>
       </c>
       <c r="F24">
-        <v>0.5963588626355912</v>
+        <v>-0.4157456197150005</v>
       </c>
       <c r="G24">
-        <v>-6.860507572065261</v>
+        <v>-5.566057781845912</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.700354620452449</v>
       </c>
       <c r="E25">
-        <v>-29.77108231251204</v>
+        <v>-29.26686390260199</v>
       </c>
       <c r="F25">
-        <v>0.4382733381564256</v>
+        <v>-0.5439173150103881</v>
       </c>
       <c r="G25">
-        <v>-6.625697198055835</v>
+        <v>-5.845663147547218</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.400943175340535</v>
       </c>
       <c r="E26">
-        <v>-29.35898664934003</v>
+        <v>-29.83050494844069</v>
       </c>
       <c r="F26">
-        <v>0.6547310952668584</v>
+        <v>-0.6251851840611634</v>
       </c>
       <c r="G26">
-        <v>-6.068618457980515</v>
+        <v>-4.960972820905622</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.179135834588445</v>
       </c>
       <c r="E27">
-        <v>-30.51341694269341</v>
+        <v>-28.90556413237402</v>
       </c>
       <c r="F27">
-        <v>0.1380003210302332</v>
+        <v>0.02136829888769509</v>
       </c>
       <c r="G27">
-        <v>-6.244663338122338</v>
+        <v>-5.98678508279527</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.030187357191696</v>
       </c>
       <c r="E28">
-        <v>-29.45472085409919</v>
+        <v>-29.70246008163681</v>
       </c>
       <c r="F28">
-        <v>0.6172431925424913</v>
+        <v>-0.5972399013302766</v>
       </c>
       <c r="G28">
-        <v>-5.846709279937627</v>
+        <v>-5.249748397750708</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.946519428189</v>
       </c>
       <c r="E29">
-        <v>-30.19612941134599</v>
+        <v>-29.82759766812777</v>
       </c>
       <c r="F29">
-        <v>0.4694406705722739</v>
+        <v>-0.9090937679631199</v>
       </c>
       <c r="G29">
-        <v>-6.180524828844498</v>
+        <v>-4.851655296653347</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.913458672559771</v>
       </c>
       <c r="E30">
-        <v>-29.5247491761538</v>
+        <v>-29.12209764552479</v>
       </c>
       <c r="F30">
-        <v>0.346134911702074</v>
+        <v>-0.1481246593003809</v>
       </c>
       <c r="G30">
-        <v>-6.435059433176903</v>
+        <v>-5.187357856517603</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.924537467846864</v>
       </c>
       <c r="E31">
-        <v>-29.60742099763783</v>
+        <v>-29.57855876854995</v>
       </c>
       <c r="F31">
-        <v>0.3511679291013405</v>
+        <v>-0.1818837264468459</v>
       </c>
       <c r="G31">
-        <v>-6.580352655804437</v>
+        <v>-6.22580316018511</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.965418192360311</v>
       </c>
       <c r="E32">
-        <v>-29.43816022465314</v>
+        <v>-28.08234189946764</v>
       </c>
       <c r="F32">
-        <v>0.2513176466917565</v>
+        <v>-0.5472866493454855</v>
       </c>
       <c r="G32">
-        <v>-7.145989156098772</v>
+        <v>-4.9943199461227</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.027949516847571</v>
       </c>
       <c r="E33">
-        <v>-28.16570657747485</v>
+        <v>-28.21989429745063</v>
       </c>
       <c r="F33">
-        <v>0.4528869844911431</v>
+        <v>-0.5124601644120144</v>
       </c>
       <c r="G33">
-        <v>-6.585712429032517</v>
+        <v>-5.300369949591704</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.104776964404605</v>
       </c>
       <c r="E34">
-        <v>-27.58267913440931</v>
+        <v>-28.17028939317061</v>
       </c>
       <c r="F34">
-        <v>0.1874190722685634</v>
+        <v>-0.425429189534955</v>
       </c>
       <c r="G34">
-        <v>-7.035109054351962</v>
+        <v>-5.413100646294966</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.189166069877137</v>
       </c>
       <c r="E35">
-        <v>-28.00191620109142</v>
+        <v>-27.64864088680504</v>
       </c>
       <c r="F35">
-        <v>0.006814833377764291</v>
+        <v>-0.5706922390697652</v>
       </c>
       <c r="G35">
-        <v>-6.008104996068177</v>
+        <v>-5.619787935948284</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.28235689926057</v>
       </c>
       <c r="E36">
-        <v>-27.35008312395334</v>
+        <v>-28.03577560124677</v>
       </c>
       <c r="F36">
-        <v>0.423369081786225</v>
+        <v>-0.3831339475042714</v>
       </c>
       <c r="G36">
-        <v>-5.90815631569204</v>
+        <v>-5.656786592895179</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.380972723558241</v>
       </c>
       <c r="E37">
-        <v>-27.19646370019114</v>
+        <v>-27.29457761804132</v>
       </c>
       <c r="F37">
-        <v>0.1322585952338075</v>
+        <v>-0.5329517352518853</v>
       </c>
       <c r="G37">
-        <v>-5.369610009545561</v>
+        <v>-4.86181867145891</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.489981250772125</v>
       </c>
       <c r="E38">
-        <v>-26.58950780046907</v>
+        <v>-26.59271848854051</v>
       </c>
       <c r="F38">
-        <v>0.1287981978085723</v>
+        <v>-0.4100300250661795</v>
       </c>
       <c r="G38">
-        <v>-6.046467597777251</v>
+        <v>-5.558589191109317</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.610872489218441</v>
       </c>
       <c r="E39">
-        <v>-25.95039067834453</v>
+        <v>-25.8593955216344</v>
       </c>
       <c r="F39">
-        <v>-0.007128905354722324</v>
+        <v>-0.2298399252722678</v>
       </c>
       <c r="G39">
-        <v>-6.117624463598346</v>
+        <v>-4.869343541469673</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.745689854101204</v>
       </c>
       <c r="E40">
-        <v>-26.11750495464959</v>
+        <v>-25.12475476879207</v>
       </c>
       <c r="F40">
-        <v>0.2103590524537038</v>
+        <v>-0.4627793098446789</v>
       </c>
       <c r="G40">
-        <v>-5.995773213934391</v>
+        <v>-5.331661226028895</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.901055665665872</v>
       </c>
       <c r="E41">
-        <v>-26.52275809359601</v>
+        <v>-24.58673130041476</v>
       </c>
       <c r="F41">
-        <v>0.1288916364575832</v>
+        <v>0.1272303289522872</v>
       </c>
       <c r="G41">
-        <v>-5.996614092501366</v>
+        <v>-3.951120699060799</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.075515422108388</v>
       </c>
       <c r="E42">
-        <v>-24.09559112343886</v>
+        <v>-24.31221520606978</v>
       </c>
       <c r="F42">
-        <v>-0.09644200045592996</v>
+        <v>0.04932862682477854</v>
       </c>
       <c r="G42">
-        <v>-5.208611558879724</v>
+        <v>-4.284353591952758</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.275125129133901</v>
       </c>
       <c r="E43">
-        <v>-24.38294091312158</v>
+        <v>-24.35582893923765</v>
       </c>
       <c r="F43">
-        <v>0.283272872800536</v>
+        <v>-0.1796111084581903</v>
       </c>
       <c r="G43">
-        <v>-5.996319453948371</v>
+        <v>-4.644653505173799</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.496018652891294</v>
       </c>
       <c r="E44">
-        <v>-23.11844153053776</v>
+        <v>-23.37851179279827</v>
       </c>
       <c r="F44">
-        <v>0.3779959073088848</v>
+        <v>-0.5987127478316353</v>
       </c>
       <c r="G44">
-        <v>-5.649278275612112</v>
+        <v>-5.327960036115989</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.73863453133006</v>
       </c>
       <c r="E45">
-        <v>-23.36923294955655</v>
+        <v>-22.33838018339848</v>
       </c>
       <c r="F45">
-        <v>0.1573294517281716</v>
+        <v>-0.6114085263027556</v>
       </c>
       <c r="G45">
-        <v>-6.002784949386568</v>
+        <v>-5.335047914115569</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.997928280485478</v>
       </c>
       <c r="E46">
-        <v>-23.63037646015688</v>
+        <v>-22.37151955618662</v>
       </c>
       <c r="F46">
-        <v>0.04076790449887061</v>
+        <v>-0.9472579131133797</v>
       </c>
       <c r="G46">
-        <v>-5.928420164937919</v>
+        <v>-5.440508652814592</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.26488403721443</v>
       </c>
       <c r="E47">
-        <v>-21.89330364402861</v>
+        <v>-22.06966053578333</v>
       </c>
       <c r="F47">
-        <v>0.2105783957229922</v>
+        <v>-0.4375952183773608</v>
       </c>
       <c r="G47">
-        <v>-6.13368392000935</v>
+        <v>-4.858749795744005</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.53720329405699</v>
       </c>
       <c r="E48">
-        <v>-23.24913781887313</v>
+        <v>-21.48682781710012</v>
       </c>
       <c r="F48">
-        <v>0.3556125997530213</v>
+        <v>-0.625836087192409</v>
       </c>
       <c r="G48">
-        <v>-5.807277372019368</v>
+        <v>-5.025720470562687</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.80310258448368</v>
       </c>
       <c r="E49">
-        <v>-21.76351305049477</v>
+        <v>-21.46193026700595</v>
       </c>
       <c r="F49">
-        <v>0.2906481912487375</v>
+        <v>-0.1886429832939414</v>
       </c>
       <c r="G49">
-        <v>-6.739344915873475</v>
+        <v>-5.915386547149808</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.06279814167396</v>
       </c>
       <c r="E50">
-        <v>-21.49155554396413</v>
+        <v>-19.62402192014889</v>
       </c>
       <c r="F50">
-        <v>0.02422688806506329</v>
+        <v>-0.3181917108828037</v>
       </c>
       <c r="G50">
-        <v>-5.900426191857842</v>
+        <v>-7.472438741180765</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.31010190609864</v>
       </c>
       <c r="E51">
-        <v>-21.13384232515023</v>
+        <v>-20.16945850047675</v>
       </c>
       <c r="F51">
-        <v>0.1078418092825198</v>
+        <v>0.06154375055056299</v>
       </c>
       <c r="G51">
-        <v>-6.378174329175606</v>
+        <v>-6.093745498623583</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.54670835002775</v>
       </c>
       <c r="E52">
-        <v>-20.17560816817917</v>
+        <v>-19.48094025540254</v>
       </c>
       <c r="F52">
-        <v>0.0413016133923737</v>
+        <v>-0.2847644301256232</v>
       </c>
       <c r="G52">
-        <v>-6.785248940321009</v>
+        <v>-6.20445676254789</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.773310683545</v>
       </c>
       <c r="E53">
-        <v>-21.27074262287611</v>
+        <v>-21.16561409878805</v>
       </c>
       <c r="F53">
-        <v>0.06409589263329367</v>
+        <v>-0.6654477395493804</v>
       </c>
       <c r="G53">
-        <v>-6.794611163106068</v>
+        <v>-5.760141824631225</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.98938967603964</v>
       </c>
       <c r="E54">
-        <v>-19.87986711616024</v>
+        <v>-18.00562682233964</v>
       </c>
       <c r="F54">
-        <v>-0.1158748638913297</v>
+        <v>-0.4877052572477804</v>
       </c>
       <c r="G54">
-        <v>-6.974810777899677</v>
+        <v>-6.095841073949941</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.2029877207047</v>
       </c>
       <c r="E55">
-        <v>-19.93614246265356</v>
+        <v>-18.240813119928</v>
       </c>
       <c r="F55">
-        <v>-0.1016595195943452</v>
+        <v>-0.8041138620934276</v>
       </c>
       <c r="G55">
-        <v>-7.406022576571907</v>
+        <v>-5.469429578645665</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.41046499179953</v>
       </c>
       <c r="E56">
-        <v>-18.77486964507459</v>
+        <v>-19.18255004608912</v>
       </c>
       <c r="F56">
-        <v>0.05095350909401941</v>
+        <v>-0.4561134916465943</v>
       </c>
       <c r="G56">
-        <v>-6.870180986131011</v>
+        <v>-6.470452475537251</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.61666014671148</v>
       </c>
       <c r="E57">
-        <v>-18.78665273444255</v>
+        <v>-18.16554535344651</v>
       </c>
       <c r="F57">
-        <v>0.08300059014589435</v>
+        <v>-0.5398273944837657</v>
       </c>
       <c r="G57">
-        <v>-6.816689191307468</v>
+        <v>-6.115909601009004</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.81602900873504</v>
       </c>
       <c r="E58">
-        <v>-17.84642379012598</v>
+        <v>-18.11023910039084</v>
       </c>
       <c r="F58">
-        <v>0.06489566412059058</v>
+        <v>-0.7633967830074794</v>
       </c>
       <c r="G58">
-        <v>-7.419476633643504</v>
+        <v>-6.956172406513581</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-13.00957402154586</v>
       </c>
       <c r="E59">
-        <v>-18.08178216972663</v>
+        <v>-17.03904215929843</v>
       </c>
       <c r="F59">
-        <v>0.2908786204594339</v>
+        <v>-0.5330047894000526</v>
       </c>
       <c r="G59">
-        <v>-8.079423955260598</v>
+        <v>-7.783537326597157</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-13.19585357731165</v>
       </c>
       <c r="E60">
-        <v>-17.60113899550052</v>
+        <v>-16.68128365574446</v>
       </c>
       <c r="F60">
-        <v>-0.2292309903477813</v>
+        <v>-0.4920984574572094</v>
       </c>
       <c r="G60">
-        <v>-7.682893431657773</v>
+        <v>-6.888137385136019</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.37213704452675</v>
       </c>
       <c r="E61">
-        <v>-18.26360492960861</v>
+        <v>-16.48544074033474</v>
       </c>
       <c r="F61">
-        <v>-0.1585699916656618</v>
+        <v>-0.3943220379438934</v>
       </c>
       <c r="G61">
-        <v>-7.74705180420885</v>
+        <v>-6.743655246165606</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.54378187317396</v>
       </c>
       <c r="E62">
-        <v>-17.30919733317403</v>
+        <v>-15.97105590627747</v>
       </c>
       <c r="F62">
-        <v>0.09179728465320276</v>
+        <v>-0.7262351237016927</v>
       </c>
       <c r="G62">
-        <v>-7.193369683856822</v>
+        <v>-7.645623309976658</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.70589759173913</v>
       </c>
       <c r="E63">
-        <v>-16.53385918442475</v>
+        <v>-16.65716500317961</v>
       </c>
       <c r="F63">
-        <v>-0.1418721883462259</v>
+        <v>-0.5560421674989925</v>
       </c>
       <c r="G63">
-        <v>-7.533836118752088</v>
+        <v>-8.581279485195335</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.86517394797698</v>
       </c>
       <c r="E64">
-        <v>-16.64482491150871</v>
+        <v>-16.97966480810986</v>
       </c>
       <c r="F64">
-        <v>-0.06388338239336808</v>
+        <v>-0.8267394766543532</v>
       </c>
       <c r="G64">
-        <v>-8.532025188662058</v>
+        <v>-8.731131329030445</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.01808408592</v>
       </c>
       <c r="E65">
-        <v>-16.31994765772443</v>
+        <v>-16.24556294367443</v>
       </c>
       <c r="F65">
-        <v>-0.3659024352913325</v>
+        <v>-0.6490983515313413</v>
       </c>
       <c r="G65">
-        <v>-7.969401284808459</v>
+        <v>-7.248731936910054</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-14.16741132165048</v>
       </c>
       <c r="E66">
-        <v>-16.7615418005824</v>
+        <v>-16.99656507310648</v>
       </c>
       <c r="F66">
-        <v>-0.1493005609425947</v>
+        <v>-0.546432240004106</v>
       </c>
       <c r="G66">
-        <v>-8.866552504859872</v>
+        <v>-8.089100679871887</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.31117416586913</v>
       </c>
       <c r="E67">
-        <v>-16.71716728378124</v>
+        <v>-16.8521656224239</v>
       </c>
       <c r="F67">
-        <v>-0.2744972646758293</v>
+        <v>-0.6974370153353419</v>
       </c>
       <c r="G67">
-        <v>-8.861172868358556</v>
+        <v>-8.193240510900742</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-14.44560019255652</v>
       </c>
       <c r="E68">
-        <v>-16.98102787878617</v>
+        <v>-16.11709919302484</v>
       </c>
       <c r="F68">
-        <v>-0.6335899113544005</v>
+        <v>-0.7870359693542863</v>
       </c>
       <c r="G68">
-        <v>-7.993207417781359</v>
+        <v>-7.787937041618848</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-14.57211103595863</v>
       </c>
       <c r="E69">
-        <v>-16.86608162304947</v>
+        <v>-15.55428685792955</v>
       </c>
       <c r="F69">
-        <v>-0.5952111740525986</v>
+        <v>-1.114734021818144</v>
       </c>
       <c r="G69">
-        <v>-8.729975948637239</v>
+        <v>-7.628749459362993</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-14.68093017984415</v>
       </c>
       <c r="E70">
-        <v>-16.61200253190111</v>
+        <v>-16.19993403957315</v>
       </c>
       <c r="F70">
-        <v>-0.6877130610145437</v>
+        <v>-1.253413605862472</v>
       </c>
       <c r="G70">
-        <v>-8.849768038975768</v>
+        <v>-7.909056660718624</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-14.77379004407562</v>
       </c>
       <c r="E71">
-        <v>-16.77861414759132</v>
+        <v>-15.46873039850263</v>
       </c>
       <c r="F71">
-        <v>-0.8729591419434958</v>
+        <v>-0.9039047555311825</v>
       </c>
       <c r="G71">
-        <v>-9.186556457776904</v>
+        <v>-8.1807100960346</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-14.84282839263983</v>
       </c>
       <c r="E72">
-        <v>-16.50479090976951</v>
+        <v>-15.07763326930419</v>
       </c>
       <c r="F72">
-        <v>-0.8791237172193438</v>
+        <v>-1.151870341829283</v>
       </c>
       <c r="G72">
-        <v>-8.768007495792387</v>
+        <v>-8.030504023826788</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-14.88849892216663</v>
       </c>
       <c r="E73">
-        <v>-16.5631719966764</v>
+        <v>-17.01164489155203</v>
       </c>
       <c r="F73">
-        <v>-1.099166192669374</v>
+        <v>-1.356114558919847</v>
       </c>
       <c r="G73">
-        <v>-8.133084587906644</v>
+        <v>-7.341966830932548</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.90868808878102</v>
       </c>
       <c r="E74">
-        <v>-16.4657554638234</v>
+        <v>-15.20468413606339</v>
       </c>
       <c r="F74">
-        <v>-0.9847608610439436</v>
+        <v>-1.863161763336518</v>
       </c>
       <c r="G74">
-        <v>-8.968249153280745</v>
+        <v>-8.43680727786154</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.90148896887612</v>
       </c>
       <c r="E75">
-        <v>-18.00482075396627</v>
+        <v>-17.2757681380494</v>
       </c>
       <c r="F75">
-        <v>-1.109982904071825</v>
+        <v>-1.242155040509613</v>
       </c>
       <c r="G75">
-        <v>-8.424349694997263</v>
+        <v>-7.563938909340681</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.871884502278</v>
       </c>
       <c r="E76">
-        <v>-17.06937840667582</v>
+        <v>-16.63125760338173</v>
       </c>
       <c r="F76">
-        <v>-0.7733575013626358</v>
+        <v>-1.27875052495063</v>
       </c>
       <c r="G76">
-        <v>-8.315568479122351</v>
+        <v>-8.193055120350541</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-14.81531398187939</v>
       </c>
       <c r="E77">
-        <v>-16.91843983952616</v>
+        <v>-16.68590722770629</v>
       </c>
       <c r="F77">
-        <v>-1.41861709657858</v>
+        <v>-1.293668242821112</v>
       </c>
       <c r="G77">
-        <v>-8.449188718178414</v>
+        <v>-7.48740571756381</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-14.73899189170624</v>
       </c>
       <c r="E78">
-        <v>-17.0131030601825</v>
+        <v>-17.26491338585302</v>
       </c>
       <c r="F78">
-        <v>-1.031051001246323</v>
+        <v>-1.223238465202646</v>
       </c>
       <c r="G78">
-        <v>-7.996435199682148</v>
+        <v>-7.907570225771491</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-14.63951523360253</v>
       </c>
       <c r="E79">
-        <v>-18.18973646159549</v>
+        <v>-18.19219995145566</v>
       </c>
       <c r="F79">
-        <v>-1.10840474112709</v>
+        <v>-1.308494897601456</v>
       </c>
       <c r="G79">
-        <v>-7.940543259342633</v>
+        <v>-7.284515623644036</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-14.52131209086122</v>
       </c>
       <c r="E80">
-        <v>-19.70047161834638</v>
+        <v>-17.90199269467411</v>
       </c>
       <c r="F80">
-        <v>-1.278725977508941</v>
+        <v>-1.906684377451667</v>
       </c>
       <c r="G80">
-        <v>-7.404377235438889</v>
+        <v>-7.294304906803661</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-14.38477628764014</v>
       </c>
       <c r="E81">
-        <v>-20.39683770887589</v>
+        <v>-18.87059705712273</v>
       </c>
       <c r="F81">
-        <v>-0.9350483323582993</v>
+        <v>-1.536185088917143</v>
       </c>
       <c r="G81">
-        <v>-7.91588962671168</v>
+        <v>-8.330604976961721</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-14.2290778423172</v>
       </c>
       <c r="E82">
-        <v>-19.9784927515733</v>
+        <v>-20.20049666132532</v>
       </c>
       <c r="F82">
-        <v>-1.585891282779126</v>
+        <v>-1.596248719466099</v>
       </c>
       <c r="G82">
-        <v>-7.727330884431411</v>
+        <v>-7.383398308356528</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-14.05836014486459</v>
       </c>
       <c r="E83">
-        <v>-19.60648314031718</v>
+        <v>-19.50722351854305</v>
       </c>
       <c r="F83">
-        <v>-1.284466119599451</v>
+        <v>-1.590604391583473</v>
       </c>
       <c r="G83">
-        <v>-7.301028624793921</v>
+        <v>-7.706411547168756</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-13.86758964949849</v>
       </c>
       <c r="E84">
-        <v>-21.25612018030535</v>
+        <v>-21.45661836699495</v>
       </c>
       <c r="F84">
-        <v>-1.432282894922907</v>
+        <v>-1.665470129471085</v>
       </c>
       <c r="G84">
-        <v>-8.166170180026121</v>
+        <v>-6.540675767516271</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-13.6636567789099</v>
       </c>
       <c r="E85">
-        <v>-22.07878993938279</v>
+        <v>-22.51475066057522</v>
       </c>
       <c r="F85">
-        <v>-1.653835433963309</v>
+        <v>-1.49492796611403</v>
       </c>
       <c r="G85">
-        <v>-7.685111497169085</v>
+        <v>-7.541983371324235</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.4423107741761</v>
       </c>
       <c r="E86">
-        <v>-23.12859436926296</v>
+        <v>-24.42380586256679</v>
       </c>
       <c r="F86">
-        <v>-1.693791542356888</v>
+        <v>-1.4219785123841</v>
       </c>
       <c r="G86">
-        <v>-7.426988261472111</v>
+        <v>-7.09449030968987</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-13.20899781825551</v>
       </c>
       <c r="E87">
-        <v>-24.81977110132348</v>
+        <v>-24.47814755065884</v>
       </c>
       <c r="F87">
-        <v>-1.682234448438969</v>
+        <v>-1.632845787613032</v>
       </c>
       <c r="G87">
-        <v>-7.463530063134586</v>
+        <v>-6.352577191065961</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-12.96453829522661</v>
       </c>
       <c r="E88">
-        <v>-25.5453639630985</v>
+        <v>-25.03183501062868</v>
       </c>
       <c r="F88">
-        <v>-1.664990266578706</v>
+        <v>-1.825096599805973</v>
       </c>
       <c r="G88">
-        <v>-6.69430494381169</v>
+        <v>-6.288243359601305</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-12.70904140248127</v>
       </c>
       <c r="E89">
-        <v>-26.99003321255148</v>
+        <v>-26.49632991928725</v>
       </c>
       <c r="F89">
-        <v>-1.574331813302333</v>
+        <v>-1.959013188309617</v>
       </c>
       <c r="G89">
-        <v>-7.52006424930872</v>
+        <v>-6.411865751128769</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-12.44544623687969</v>
       </c>
       <c r="E90">
-        <v>-28.51623310803857</v>
+        <v>-28.93295234317241</v>
       </c>
       <c r="F90">
-        <v>-1.634196688758902</v>
+        <v>-1.316374626383725</v>
       </c>
       <c r="G90">
-        <v>-7.467479543962937</v>
+        <v>-6.439872966391003</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.16753941639042</v>
       </c>
       <c r="E91">
-        <v>-30.0988374115282</v>
+        <v>-29.50932519368368</v>
       </c>
       <c r="F91">
-        <v>-1.73920589318803</v>
+        <v>-2.092524348098909</v>
       </c>
       <c r="G91">
-        <v>-7.091517439795604</v>
+        <v>-5.857538074396584</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-11.87858326060429</v>
       </c>
       <c r="E92">
-        <v>-32.03250939822546</v>
+        <v>-31.20148460460387</v>
       </c>
       <c r="F92">
-        <v>-1.559810813763669</v>
+        <v>-1.961582751157418</v>
       </c>
       <c r="G92">
-        <v>-7.00573127323647</v>
+        <v>-6.832308345161749</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-11.56967027001089</v>
       </c>
       <c r="E93">
-        <v>-32.58139441151017</v>
+        <v>-33.89276802854738</v>
       </c>
       <c r="F93">
-        <v>-2.051928422515492</v>
+        <v>-2.213883732399033</v>
       </c>
       <c r="G93">
-        <v>-6.789277874242302</v>
+        <v>-7.022750787853863</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-11.24127647080781</v>
       </c>
       <c r="E94">
-        <v>-35.00581033370766</v>
+        <v>-34.63587249931005</v>
       </c>
       <c r="F94">
-        <v>-2.198482192371385</v>
+        <v>-1.874638880105707</v>
       </c>
       <c r="G94">
-        <v>-6.999997408362453</v>
+        <v>-7.568957696378217</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.89046267942966</v>
       </c>
       <c r="E95">
-        <v>-37.24358519967902</v>
+        <v>-36.89964986303345</v>
       </c>
       <c r="F95">
-        <v>-1.913956755015365</v>
+        <v>-1.69096066803304</v>
       </c>
       <c r="G95">
-        <v>-6.422393285943651</v>
+        <v>-6.131806840688584</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.5145886989253</v>
       </c>
       <c r="E96">
-        <v>-39.77021330870363</v>
+        <v>-39.75605503471865</v>
       </c>
       <c r="F96">
-        <v>-1.957578350750229</v>
+        <v>-1.574688147133307</v>
       </c>
       <c r="G96">
-        <v>-6.689647006237935</v>
+        <v>-7.113721268727496</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.12090368007484</v>
       </c>
       <c r="E97">
-        <v>-40.99521760522956</v>
+        <v>-41.31325912749925</v>
       </c>
       <c r="F97">
-        <v>-1.927995516102778</v>
+        <v>-1.954620779953146</v>
       </c>
       <c r="G97">
-        <v>-7.548938827502243</v>
+        <v>-7.007601731466158</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.70667984217417</v>
       </c>
       <c r="E98">
-        <v>-44.10837366772763</v>
+        <v>-42.84199043995662</v>
       </c>
       <c r="F98">
-        <v>-2.45480816219709</v>
+        <v>-2.015964044881777</v>
       </c>
       <c r="G98">
-        <v>-7.400292022243428</v>
+        <v>-7.209607909726947</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.292208351919069</v>
       </c>
       <c r="E99">
-        <v>-45.61872163995087</v>
+        <v>-45.44833327693827</v>
       </c>
       <c r="F99">
-        <v>-2.413041877942164</v>
+        <v>-2.019486998690672</v>
       </c>
       <c r="G99">
-        <v>-8.220337326139676</v>
+        <v>-6.942877255627868</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.876913528150602</v>
       </c>
       <c r="E100">
-        <v>-48.58973343182219</v>
+        <v>-46.68618258998694</v>
       </c>
       <c r="F100">
-        <v>-2.284745069879456</v>
+        <v>-2.300338238322873</v>
       </c>
       <c r="G100">
-        <v>-7.629692964841686</v>
+        <v>-7.962369686083047</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.496160858795836</v>
       </c>
       <c r="E101">
-        <v>-50.09738809412936</v>
+        <v>-50.93179792207169</v>
       </c>
       <c r="F101">
-        <v>-2.436186948043353</v>
+        <v>-2.343198863365369</v>
       </c>
       <c r="G101">
-        <v>-7.109225547885166</v>
+        <v>-7.76189960095248</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.144620282052367</v>
       </c>
       <c r="E102">
-        <v>-51.66148452434964</v>
+        <v>-51.74615453498956</v>
       </c>
       <c r="F102">
-        <v>-2.142171152989062</v>
+        <v>-2.181873868436171</v>
       </c>
       <c r="G102">
-        <v>-8.130747342755919</v>
+        <v>-7.26642018172638</v>
       </c>
     </row>
   </sheetData>
